--- a/data/source/team_default.xlsx
+++ b/data/source/team_default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/Dada/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D699408-BA55-4608-91CE-19256F248B0E}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0361C073-C0BE-413A-BD2A-F122C0E48905}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>team_id</t>
   </si>
@@ -177,6 +177,12 @@
   </si>
   <si>
     <t>france.png</t>
+  </si>
+  <si>
+    <t>prestige</t>
+  </si>
+  <si>
+    <t>finance</t>
   </si>
 </sst>
 </file>
@@ -233,7 +239,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -249,6 +255,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -539,7 +549,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -549,7 +559,7 @@
     <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,8 +587,14 @@
       <c r="I1" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -606,8 +622,14 @@
       <c r="I2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -635,8 +657,14 @@
       <c r="I3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -664,8 +692,14 @@
       <c r="I4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -693,8 +727,14 @@
       <c r="I5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -722,8 +762,14 @@
       <c r="I6" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -751,8 +797,14 @@
       <c r="I7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -780,8 +832,14 @@
       <c r="I8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -809,8 +867,14 @@
       <c r="I9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -838,8 +902,14 @@
       <c r="I10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J10">
+        <v>8</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -867,8 +937,14 @@
       <c r="I11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11">
+        <v>7</v>
+      </c>
+      <c r="K11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -895,6 +971,12 @@
       </c>
       <c r="I12" t="s">
         <v>46</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/source/team_default.xlsx
+++ b/data/source/team_default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/Dada/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="292" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0361C073-C0BE-413A-BD2A-F122C0E48905}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE6D72E4-4779-4D68-BD84-9412AA951153}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -763,7 +763,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -906,7 +906,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/data/source/team_default.xlsx
+++ b/data/source/team_default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/Dada/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE6D72E4-4779-4D68-BD84-9412AA951153}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65D0346E-1EDB-4418-B99A-87CA0BADF2F0}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -693,7 +693,7 @@
         <v>44</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -763,7 +763,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -798,7 +798,7 @@
         <v>45</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -833,7 +833,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>9</v>
@@ -868,7 +868,7 @@
         <v>46</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -903,7 +903,7 @@
         <v>43</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>9</v>
@@ -973,7 +973,7 @@
         <v>46</v>
       </c>
       <c r="J12">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <v>8</v>
